--- a/basedatos_partidas/salida/descompuestos/07.09.01.010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.09.01.010.xlsx
@@ -558,10 +558,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="H10" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -717,10 +717,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>63.95</v>
+        <v>53.95</v>
       </c>
       <c r="H20" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="21">
@@ -736,7 +736,7 @@
       </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="5" t="n">
-        <v>64.59</v>
+        <v>54.49</v>
       </c>
     </row>
   </sheetData>
